--- a/DataFile/ExcelSheet.xlsx
+++ b/DataFile/ExcelSheet.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Users\Pankaj\eclipse-workspace\Project\DataFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72773B14-8492-442A-9E91-10025FF22A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F67DFCC-E2C6-4FDE-A095-DA966B60F099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Search" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="5" r:id="rId1"/>
+    <sheet name="Invalid_login" sheetId="6" r:id="rId2"/>
+    <sheet name="Search" sheetId="1" r:id="rId3"/>
+    <sheet name="Invalid_Search" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,22 +28,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>ProductName</t>
   </si>
   <si>
     <t>Shoes</t>
+  </si>
+  <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>testing@gmail.com</t>
+  </si>
+  <si>
+    <t>testing1@gmail.com</t>
+  </si>
+  <si>
+    <t>Chair</t>
+  </si>
+  <si>
+    <t>Tables</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>pm1494065@gmail.com</t>
+  </si>
+  <si>
+    <t>ok</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -63,10 +101,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -74,8 +113,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -353,8 +394,93 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1702F8B2-E3C7-4E5D-B016-94DF8BFAC30A}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{9D4AA392-0BA7-4569-9085-159F28A9407B}"/>
+    <hyperlink ref="B2" r:id="rId2" display="psit@12345" xr:uid="{42C72DED-C969-487C-ABFB-B79046F83307}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{044CF0A5-F790-4D12-856F-E4146B7BF673}"/>
+    <hyperlink ref="B3" r:id="rId4" display="psit@12345" xr:uid="{7790C05B-22D4-435F-AB50-C8BABE7295EE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3C50C4-9A59-46F8-95F8-2C1E3E35DB2F}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>12345</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="psit@12345" xr:uid="{F1A5651F-2367-4F7E-A55E-55D32D864445}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{3CA128F3-7534-4B7A-A188-421E2D7CA002}"/>
+    <hyperlink ref="A2" r:id="rId3" xr:uid="{685B27FC-4403-4F52-B1D8-1BC6D8C6CC7C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.77734375" customWidth="1"/>
@@ -371,8 +497,56 @@
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37F95E10-42FB-444B-B65B-CC21B040AD47}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>89732</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>888888</v>
+        <v>89754</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>89213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>89021</v>
       </c>
     </row>
   </sheetData>
